--- a/src/download/dist2.xlsx
+++ b/src/download/dist2.xlsx
@@ -1290,7 +1290,7 @@
     <row r="2" ht="20" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月19日 19时</t>
+          <t>填报日期：2025年03月19日 20时</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>今日19时</t>
+          <t>今日20时</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>今日15时</t>
+          <t>今日16时</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>今日11时</t>
+          <t>今日12时</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">

--- a/src/download/dist2.xlsx
+++ b/src/download/dist2.xlsx
@@ -1290,7 +1290,7 @@
     <row r="2" ht="20" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月19日 20时</t>
+          <t>填报日期：2025年03月20日 15时</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>今日20时</t>
+          <t>今日15时</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>今日16时</t>
+          <t>今日11时</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>今日12时</t>
+          <t>今日07时</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E5" s="29" t="n">
         <v>5.71</v>
       </c>
-      <c r="E5" s="29" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F5" s="29" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>44025</v>
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="D6" s="29" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E6" s="29" t="n">
         <v>4.66</v>
       </c>
-      <c r="E6" s="29" t="n">
-        <v>4.52</v>
-      </c>
       <c r="F6" s="29" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>44033</v>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="E7" s="29" t="n">
         <v>4.76</v>
       </c>
-      <c r="E7" s="29" t="n">
-        <v>4.63</v>
-      </c>
       <c r="F7" s="29" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>44033</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="D8" s="29" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E8" s="29" t="n">
         <v>4.15</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>4.13</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>3.96</v>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="E9" s="29" t="n">
         <v>4.76</v>
       </c>
-      <c r="E9" s="29" t="n">
-        <v>4.63</v>
-      </c>
       <c r="F9" s="29" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>44033</v>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D10" s="29" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E10" s="29" t="n">
         <v>8.34</v>
       </c>
-      <c r="E10" s="29" t="n">
-        <v>8.460000000000001</v>
-      </c>
       <c r="F10" s="29" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>44033</v>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <v>7.19</v>
       </c>
-      <c r="E11" s="29" t="n">
-        <v>7.2</v>
-      </c>
       <c r="F11" s="29" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>44030</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="D12" s="29" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E12" s="29" t="n">
         <v>5.71</v>
       </c>
-      <c r="E12" s="29" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F12" s="29" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>44025</v>
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <v>5.71</v>
       </c>
-      <c r="E13" s="29" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F13" s="29" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>44025</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D14" s="29" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E14" s="29" t="n">
         <v>5.71</v>
       </c>
-      <c r="E14" s="29" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F14" s="29" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>44025</v>

--- a/src/download/dist2.xlsx
+++ b/src/download/dist2.xlsx
@@ -1290,7 +1290,7 @@
     <row r="2" ht="20" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月20日 15时</t>
+          <t>填报日期：2025年03月21日 19时</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
+          <t>今日19时</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
           <t>今日15时</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>今日11时</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>今日07时</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E5" s="29" t="n">
         <v>5.74</v>
       </c>
-      <c r="E5" s="29" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F5" s="29" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>44025</v>
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="D6" s="29" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E6" s="29" t="n">
         <v>4.67</v>
       </c>
-      <c r="E6" s="29" t="n">
-        <v>4.66</v>
-      </c>
       <c r="F6" s="29" t="n">
-        <v>3.86</v>
+        <v>4.06</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>44033</v>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E7" s="29" t="n">
         <v>4.79</v>
       </c>
-      <c r="E7" s="29" t="n">
-        <v>4.76</v>
-      </c>
       <c r="F7" s="29" t="n">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>44033</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="D8" s="29" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E8" s="29" t="n">
         <v>4.18</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>4.15</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>3.96</v>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E9" s="29" t="n">
         <v>4.79</v>
       </c>
-      <c r="E9" s="29" t="n">
-        <v>4.76</v>
-      </c>
       <c r="F9" s="29" t="n">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>44033</v>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D10" s="29" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E10" s="29" t="n">
         <v>8.25</v>
       </c>
-      <c r="E10" s="29" t="n">
-        <v>8.34</v>
-      </c>
       <c r="F10" s="29" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>44033</v>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <v>7.18</v>
       </c>
-      <c r="E11" s="29" t="n">
-        <v>7.19</v>
-      </c>
       <c r="F11" s="29" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>44030</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="D12" s="29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E12" s="29" t="n">
         <v>5.74</v>
       </c>
-      <c r="E12" s="29" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F12" s="29" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>44025</v>
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <v>5.74</v>
       </c>
-      <c r="E13" s="29" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F13" s="29" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>44025</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D14" s="29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E14" s="29" t="n">
         <v>5.74</v>
       </c>
-      <c r="E14" s="29" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F14" s="29" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>44025</v>
